--- a/주유소자동화/webapp/고객등록양식.xlsx
+++ b/주유소자동화/webapp/고객등록양식.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>★ 업체명은 BOS 거래내역서의 업체명과 정확히 일치해야 합니다. 출력방법을 비워두면 기본(차량별-유종별)이 적용됩니다.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="295">
+  <si>
+    <t>★ 업체명은 BOS 거래내역서의 업체명과 정확히 일치해야 합니다. 대표자명은 세금계산서 성명란에 사용됩니다. 주소·업태·종목은 세금계산서 일괄발행 시 사용됩니다.</t>
   </si>
   <si>
     <t>업체명 *</t>
@@ -22,6 +22,9 @@
     <t>사업자번호</t>
   </si>
   <si>
+    <t>대표자명</t>
+  </si>
+  <si>
     <t>담당자명</t>
   </si>
   <si>
@@ -31,53 +34,875 @@
     <t>연락처</t>
   </si>
   <si>
+    <t>주소</t>
+  </si>
+  <si>
+    <t>업태</t>
+  </si>
+  <si>
+    <t>종목</t>
+  </si>
+  <si>
     <t>출력방법</t>
   </si>
   <si>
-    <t>출력방법 선택값: 유종별 / 판매일자순 / 차량별-판매일자순 / 차량별-유종별 (비워두면 기본 차량별-유종별)</t>
-  </si>
-  <si>
-    <t>태성화학(주)</t>
-  </si>
-  <si>
-    <t>123-45-67890</t>
-  </si>
-  <si>
-    <t>홍길동</t>
-  </si>
-  <si>
-    <t>example@company.com</t>
-  </si>
-  <si>
-    <t>010-1234-5678</t>
-  </si>
-  <si>
-    <t>차량별-유종별</t>
-  </si>
-  <si>
-    <t>(주)대한상사</t>
-  </si>
-  <si>
-    <t>234-56-78901</t>
-  </si>
-  <si>
-    <t>김철수</t>
-  </si>
-  <si>
-    <t>daehan@email.com</t>
-  </si>
-  <si>
-    <t>031-123-4567</t>
+    <t>세금계산서발행구분</t>
+  </si>
+  <si>
+    <t>출력방법: 유종별 / 판매일자순 / 차량별-판매일자순 / 차량별-유종별 (비워두면 기본)  |  세금계산서발행구분: 합산 / 분리 (비워두면 합산)</t>
+  </si>
+  <si>
+    <t>재상플랜트</t>
+  </si>
+  <si>
+    <t>533-81-00042</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>help@jsplant.co.kr</t>
+  </si>
+  <si>
+    <t>합산</t>
+  </si>
+  <si>
+    <t>태성화학주식회사</t>
+  </si>
+  <si>
+    <t>581-87-03040</t>
+  </si>
+  <si>
+    <t>임영빈</t>
+  </si>
+  <si>
+    <t>tseps88@naver.com</t>
+  </si>
+  <si>
+    <t>043-750-7234</t>
+  </si>
+  <si>
+    <t>다올이앤씨</t>
+  </si>
+  <si>
+    <t>229-81-05191</t>
+  </si>
+  <si>
+    <t>손광수</t>
+  </si>
+  <si>
+    <t>디케이산업(스마일)</t>
+  </si>
+  <si>
+    <t>878-14-02034</t>
+  </si>
+  <si>
+    <t>김병순</t>
+  </si>
+  <si>
+    <t>010-3435-0238</t>
+  </si>
+  <si>
+    <t>중앙산업</t>
+  </si>
+  <si>
+    <t>204-40-09690</t>
+  </si>
+  <si>
+    <t>윤태구</t>
+  </si>
+  <si>
+    <t>yt92000@hanmail.net</t>
+  </si>
+  <si>
+    <t>010-4876-0418</t>
+  </si>
+  <si>
+    <t>만세물류(주)</t>
+  </si>
+  <si>
+    <t>영진물산(주)</t>
+  </si>
+  <si>
+    <t>215-87-35761</t>
+  </si>
+  <si>
+    <t>조정삼님</t>
+  </si>
+  <si>
+    <t>chss7338@empas.com</t>
+  </si>
+  <si>
+    <t>010-5158-5551</t>
+  </si>
+  <si>
+    <t>한누리투어(주)</t>
+  </si>
+  <si>
+    <t>499-81-00835</t>
+  </si>
+  <si>
+    <t>최기덕,최우택</t>
+  </si>
+  <si>
+    <t>jsj4979@hanmail.net</t>
+  </si>
+  <si>
+    <t>010-6416-4553</t>
+  </si>
+  <si>
+    <t>대소방범대</t>
+  </si>
+  <si>
+    <t>우지멀티텍 방범대장님</t>
+  </si>
+  <si>
+    <t>010-4169-7709</t>
+  </si>
+  <si>
+    <t>(주)가이아글로벌</t>
+  </si>
+  <si>
+    <t>114-86-21399</t>
+  </si>
+  <si>
+    <t>황민희 차장님</t>
+  </si>
+  <si>
+    <t>mhhwang@grouphan.com</t>
+  </si>
+  <si>
+    <t>02-521-3875</t>
+  </si>
+  <si>
+    <t>(주)보정골재</t>
+  </si>
+  <si>
+    <t>756-88-01532</t>
+  </si>
+  <si>
+    <t>이정훈</t>
+  </si>
+  <si>
+    <t>bojeong1193@naver.com</t>
+  </si>
+  <si>
+    <t>(주)다성산업</t>
+  </si>
+  <si>
+    <t>224-87-01436</t>
+  </si>
+  <si>
+    <t>정희권</t>
+  </si>
+  <si>
+    <t>jhk5718@naver.com</t>
+  </si>
+  <si>
+    <t>043-532-0441</t>
+  </si>
+  <si>
+    <t>(주)메탈링크</t>
+  </si>
+  <si>
+    <t>124-86-48172</t>
+  </si>
+  <si>
+    <t>홍승완</t>
+  </si>
+  <si>
+    <t>alrod@emetallink.com</t>
+  </si>
+  <si>
+    <t>043-877-8331</t>
+  </si>
+  <si>
+    <t>(주)미래산업</t>
+  </si>
+  <si>
+    <t>841-23-00695</t>
+  </si>
+  <si>
+    <t>ZHU QINGLIN</t>
+  </si>
+  <si>
+    <t>tian1628@hanmail.net</t>
+  </si>
+  <si>
+    <t>(주)에이치스틸</t>
+  </si>
+  <si>
+    <t>441-81-02299</t>
+  </si>
+  <si>
+    <t>박준용</t>
+  </si>
+  <si>
+    <t>jyp0813@sypanel.com</t>
+  </si>
+  <si>
+    <t>010-2426-9432</t>
+  </si>
+  <si>
+    <t>(주)우리들푸드</t>
+  </si>
+  <si>
+    <t>485-81-01704</t>
+  </si>
+  <si>
+    <t>허철민</t>
+  </si>
+  <si>
+    <t>hcm312@nate.com</t>
+  </si>
+  <si>
+    <t>031-989-7203</t>
+  </si>
+  <si>
+    <t>(주)유성이엔지</t>
+  </si>
+  <si>
+    <t>785-81-00245</t>
+  </si>
+  <si>
+    <t>송수종</t>
+  </si>
+  <si>
+    <t>cmy7392@nate.com</t>
+  </si>
+  <si>
+    <t>070-8829-3171</t>
+  </si>
+  <si>
+    <t>(주)제론텍</t>
+  </si>
+  <si>
+    <t>303-81-51372</t>
+  </si>
+  <si>
+    <t>변영수 과장</t>
+  </si>
+  <si>
+    <t>zerontec@bill36524.com</t>
+  </si>
+  <si>
+    <t>010-8843-5160</t>
+  </si>
+  <si>
+    <t>(주)중앙안전유리</t>
+  </si>
+  <si>
+    <t>303-81-32166</t>
+  </si>
+  <si>
+    <t>유정호 차장님</t>
+  </si>
+  <si>
+    <t>qwert744@wehago.com</t>
+  </si>
+  <si>
+    <t>105-0339-486</t>
+  </si>
+  <si>
+    <t>(주)하나항공여행사</t>
+  </si>
+  <si>
+    <t>303-81-34693</t>
+  </si>
+  <si>
+    <t>조천행</t>
+  </si>
+  <si>
+    <t>mas99ter@nate.com</t>
+  </si>
+  <si>
+    <t>010-6308-0992</t>
+  </si>
+  <si>
+    <t>CW소방</t>
+  </si>
+  <si>
+    <t>571-87-00764</t>
+  </si>
+  <si>
+    <t>김나리 주임님</t>
+  </si>
+  <si>
+    <t>safelife.ses@gmail.com</t>
+  </si>
+  <si>
+    <t>070-5057-3945</t>
+  </si>
+  <si>
+    <t>중앙복층유리 주식회사</t>
+  </si>
+  <si>
+    <t>303-81-77071</t>
+  </si>
+  <si>
+    <t>서재관</t>
+  </si>
+  <si>
+    <t>jung1127@bill36524.com</t>
+  </si>
+  <si>
+    <t>경성물류</t>
+  </si>
+  <si>
+    <t>303-05-57163</t>
+  </si>
+  <si>
+    <t>김미영</t>
+  </si>
+  <si>
+    <t>ejs19@hanmail.net</t>
+  </si>
+  <si>
+    <t>043-537-8804</t>
+  </si>
+  <si>
+    <t>중앙크레인</t>
+  </si>
+  <si>
+    <t>301-23-93468</t>
+  </si>
+  <si>
+    <t>사장님</t>
+  </si>
+  <si>
+    <t>kimdm0978@naver.com</t>
+  </si>
+  <si>
+    <t>010-5432-0264</t>
+  </si>
+  <si>
+    <t>신성기업주식회사</t>
+  </si>
+  <si>
+    <t>303-81-73677</t>
+  </si>
+  <si>
+    <t>신주영과장님</t>
+  </si>
+  <si>
+    <t>010-7325-5200</t>
+  </si>
+  <si>
+    <t>에스로직(주)</t>
+  </si>
+  <si>
+    <t>303-81-50674</t>
+  </si>
+  <si>
+    <t>김경진 과장</t>
+  </si>
+  <si>
+    <t>kjmyfriend@naver.com</t>
+  </si>
+  <si>
+    <t>010-2500-4288</t>
   </si>
   <si>
     <t>유종별</t>
+  </si>
+  <si>
+    <t>분리</t>
+  </si>
+  <si>
+    <t>주식회사 피피이씨음성생면</t>
+  </si>
+  <si>
+    <t>303-81-35921</t>
+  </si>
+  <si>
+    <t>우연희</t>
+  </si>
+  <si>
+    <t>yeonhee.woo@pulmuone.com</t>
+  </si>
+  <si>
+    <t>010-3232-4467</t>
+  </si>
+  <si>
+    <t>대원테크</t>
+  </si>
+  <si>
+    <t>303-07-85265</t>
+  </si>
+  <si>
+    <t>김태형</t>
+  </si>
+  <si>
+    <t>043-534-5812</t>
+  </si>
+  <si>
+    <t>오미관광(주)</t>
+  </si>
+  <si>
+    <t>303-81-70613</t>
+  </si>
+  <si>
+    <t>이재진</t>
+  </si>
+  <si>
+    <t>omi3003@daum.net</t>
+  </si>
+  <si>
+    <t>043-881-3003</t>
+  </si>
+  <si>
+    <t>대창폴리마</t>
+  </si>
+  <si>
+    <t>303-05-26374</t>
+  </si>
+  <si>
+    <t>김천희</t>
+  </si>
+  <si>
+    <t>043-881-3561</t>
+  </si>
+  <si>
+    <t>명가운수</t>
+  </si>
+  <si>
+    <t>681-16-00488</t>
+  </si>
+  <si>
+    <t>정성렬</t>
+  </si>
+  <si>
+    <t>jsr0084@naver.com</t>
+  </si>
+  <si>
+    <t>(주)벽산음성베이스공장</t>
+  </si>
+  <si>
+    <t>203-81-43780</t>
+  </si>
+  <si>
+    <t>황한태</t>
+  </si>
+  <si>
+    <t>bsb01@bsco.co.kr</t>
+  </si>
+  <si>
+    <t>043-877-2917</t>
+  </si>
+  <si>
+    <t>삼동(주)</t>
+  </si>
+  <si>
+    <t>303-81-06751</t>
+  </si>
+  <si>
+    <t>이나영</t>
+  </si>
+  <si>
+    <t>leeny@samdong.com</t>
+  </si>
+  <si>
+    <t>상공회의소</t>
+  </si>
+  <si>
+    <t>삼정환경개발</t>
+  </si>
+  <si>
+    <t>303-07-18470</t>
+  </si>
+  <si>
+    <t>정택철</t>
+  </si>
+  <si>
+    <t>a8838313@nate.com</t>
+  </si>
+  <si>
+    <t>043-883-8313</t>
+  </si>
+  <si>
+    <t>서보산업(주)</t>
+  </si>
+  <si>
+    <t>303-81-32093</t>
+  </si>
+  <si>
+    <t>이범수</t>
+  </si>
+  <si>
+    <t>news4544@seobo.co.kr</t>
+  </si>
+  <si>
+    <t>010-9160-2114</t>
+  </si>
+  <si>
+    <t>웰크론</t>
+  </si>
+  <si>
+    <t>120-81-63773</t>
+  </si>
+  <si>
+    <t>이영규</t>
+  </si>
+  <si>
+    <t>whdgh2020@welcron.com</t>
+  </si>
+  <si>
+    <t>010-8841-8232</t>
+  </si>
+  <si>
+    <t>조광페인트(주)</t>
+  </si>
+  <si>
+    <t>606-81-00205</t>
+  </si>
+  <si>
+    <t>정지현 사원</t>
+  </si>
+  <si>
+    <t>jihyounj77@ckpc.co.kr</t>
+  </si>
+  <si>
+    <t>010-3437-2876</t>
+  </si>
+  <si>
+    <t>현대스크랩</t>
+  </si>
+  <si>
+    <t>126-81-90216</t>
+  </si>
+  <si>
+    <t>이석재</t>
+  </si>
+  <si>
+    <t>scrap82@hanmail.net</t>
+  </si>
+  <si>
+    <t>010-9314-0987</t>
+  </si>
+  <si>
+    <t>지성중공업</t>
+  </si>
+  <si>
+    <t>박혜정</t>
+  </si>
+  <si>
+    <t>010-3863-8329</t>
+  </si>
+  <si>
+    <t>하나엘티</t>
+  </si>
+  <si>
+    <t>303-81-58128</t>
+  </si>
+  <si>
+    <t>김수연과장</t>
+  </si>
+  <si>
+    <t>hana3990@hanmail.net</t>
+  </si>
+  <si>
+    <t>010-2872-4790</t>
+  </si>
+  <si>
+    <t>행운농장</t>
+  </si>
+  <si>
+    <t>금강어린이집</t>
+  </si>
+  <si>
+    <t>풀무원외상6576</t>
+  </si>
+  <si>
+    <t>두원종합개발주식회사</t>
+  </si>
+  <si>
+    <t>448-81-03509</t>
+  </si>
+  <si>
+    <t>박호준</t>
+  </si>
+  <si>
+    <t>singg123@naver.com</t>
+  </si>
+  <si>
+    <t>이형찬</t>
+  </si>
+  <si>
+    <t>010-2722-3836</t>
+  </si>
+  <si>
+    <t>태남메디코스(주)</t>
+  </si>
+  <si>
+    <t>303-81-77538</t>
+  </si>
+  <si>
+    <t>조택래</t>
+  </si>
+  <si>
+    <t>tax303@taenam.co.kr</t>
+  </si>
+  <si>
+    <t>직지관광</t>
+  </si>
+  <si>
+    <t>대표보관고객</t>
+  </si>
+  <si>
+    <t>그린테크</t>
+  </si>
+  <si>
+    <t>파란농장</t>
+  </si>
+  <si>
+    <t>대소파출소</t>
+  </si>
+  <si>
+    <t>삼진크레인</t>
+  </si>
+  <si>
+    <t>보관증7989</t>
+  </si>
+  <si>
+    <t>010-2753-7603</t>
+  </si>
+  <si>
+    <t>주식회사 명신</t>
+  </si>
+  <si>
+    <t>675-87-02569</t>
+  </si>
+  <si>
+    <t>도원아이디</t>
+  </si>
+  <si>
+    <t>206-86-12976</t>
+  </si>
+  <si>
+    <t>오현두</t>
+  </si>
+  <si>
+    <t>010-3161-0610</t>
+  </si>
+  <si>
+    <t>동주산업</t>
+  </si>
+  <si>
+    <t>277-03-00159</t>
+  </si>
+  <si>
+    <t>김동주</t>
+  </si>
+  <si>
+    <t>다올이앤씨(주)보수보강</t>
+  </si>
+  <si>
+    <t>디비엘(주)음성지점</t>
+  </si>
+  <si>
+    <t>131-85-31390</t>
+  </si>
+  <si>
+    <t>주재훈</t>
+  </si>
+  <si>
+    <t>bebill@dbl.kr</t>
+  </si>
+  <si>
+    <t>010-5115-0312</t>
+  </si>
+  <si>
+    <t>명성레이저</t>
+  </si>
+  <si>
+    <t>303-13-12948</t>
+  </si>
+  <si>
+    <t>박용철</t>
+  </si>
+  <si>
+    <t>mslaser2013@naver.com</t>
+  </si>
+  <si>
+    <t>043-883-5411</t>
+  </si>
+  <si>
+    <t>홍창엠앤티(주)</t>
+  </si>
+  <si>
+    <t>301-85-09518</t>
+  </si>
+  <si>
+    <t>장원철경리부장님</t>
+  </si>
+  <si>
+    <t>hc1460@hanmail.net</t>
+  </si>
+  <si>
+    <t>010-9900-8789</t>
+  </si>
+  <si>
+    <t>새한관광(자)</t>
+  </si>
+  <si>
+    <t>301-81-28900</t>
+  </si>
+  <si>
+    <t>이용태</t>
+  </si>
+  <si>
+    <t>saehanbus@naver.com</t>
+  </si>
+  <si>
+    <t>010-6391-8182</t>
+  </si>
+  <si>
+    <t>지에스켐(주)</t>
+  </si>
+  <si>
+    <t>519-85-00461</t>
+  </si>
+  <si>
+    <t>gsmg@drcc.co.kr</t>
+  </si>
+  <si>
+    <t>010-8562-6123</t>
+  </si>
+  <si>
+    <t>풀무원 8470</t>
+  </si>
+  <si>
+    <t>대신정기화물자동차음성터미널운영</t>
+  </si>
+  <si>
+    <t>105-82-77305</t>
+  </si>
+  <si>
+    <t>윤광덕</t>
+  </si>
+  <si>
+    <t>estax@idaeshin.kr</t>
+  </si>
+  <si>
+    <t>070-4313-6432</t>
+  </si>
+  <si>
+    <t>대소어린이집</t>
+  </si>
+  <si>
+    <t>(학)건국대학교건국유업.건국햄</t>
+  </si>
+  <si>
+    <t>207-82-02153</t>
+  </si>
+  <si>
+    <t>박경철</t>
+  </si>
+  <si>
+    <t>jhroh70@kkmh.co.kr</t>
+  </si>
+  <si>
+    <t>대소수영장</t>
+  </si>
+  <si>
+    <t>제이케이ENG</t>
+  </si>
+  <si>
+    <t>359-31-00207</t>
+  </si>
+  <si>
+    <t>장기봉</t>
+  </si>
+  <si>
+    <t>kjbang881100@naver.com</t>
+  </si>
+  <si>
+    <t>010-8934-0488</t>
+  </si>
+  <si>
+    <t>(주)나람</t>
+  </si>
+  <si>
+    <t>303-81-38781</t>
+  </si>
+  <si>
+    <t>이범호</t>
+  </si>
+  <si>
+    <t>naram66@naver.com</t>
+  </si>
+  <si>
+    <t>043-881-5401</t>
+  </si>
+  <si>
+    <t>동일농장</t>
+  </si>
+  <si>
+    <t>대일기계정밀</t>
+  </si>
+  <si>
+    <t>임완교</t>
+  </si>
+  <si>
+    <t>세광기전</t>
+  </si>
+  <si>
+    <t>9899박제동</t>
+  </si>
+  <si>
+    <t>3678이대원</t>
+  </si>
+  <si>
+    <t>배준용</t>
+  </si>
+  <si>
+    <t>면세박충남</t>
+  </si>
+  <si>
+    <t>조인보관증</t>
+  </si>
+  <si>
+    <t>자뎅 보관증</t>
+  </si>
+  <si>
+    <t>신창기업</t>
+  </si>
+  <si>
+    <t>비에치로지스틱스</t>
+  </si>
+  <si>
+    <t>337-81-00615</t>
+  </si>
+  <si>
+    <t>김병훈</t>
+  </si>
+  <si>
+    <t>bhlogistics@naver.com</t>
+  </si>
+  <si>
+    <t>장한주</t>
+  </si>
+  <si>
+    <t>105-4982-921</t>
+  </si>
+  <si>
+    <t>건국노사TFT</t>
+  </si>
+  <si>
+    <t>현대오일뱅크</t>
+  </si>
+  <si>
+    <t>대표면세고객</t>
+  </si>
+  <si>
+    <t>대표외상고객</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -97,10 +922,6 @@
       <i/>
       <color rgb="FF64748B"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF94A3B8"/>
     </font>
   </fonts>
   <fills count="7">
@@ -173,8 +994,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,18 +1335,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="36" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,8 +1359,13 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -554,61 +1384,3086 @@
       <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="K73" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K75" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K79" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K81" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K83" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K85" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K87" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
